--- a/Data/Skin.xlsx
+++ b/Data/Skin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F00CB23-35F6-47EC-A756-EDA89CD36E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E453C6B6-2C67-432D-B05A-B16A3FA48CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42315" yWindow="1890" windowWidth="20865" windowHeight="16680" xr2:uid="{AC506EF3-83D9-4F79-B820-BF7DB42898A7}"/>
+    <workbookView xWindow="51990" yWindow="3750" windowWidth="20865" windowHeight="16680" xr2:uid="{AC506EF3-83D9-4F79-B820-BF7DB42898A7}"/>
   </bookViews>
   <sheets>
     <sheet name="AllyArenaFakeEnemy" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>Index</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -66,18 +66,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Skin/skin_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Skin/skin_02</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Hair/001</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Hair/002</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -91,10 +83,6 @@
   </si>
   <si>
     <t>Weapon</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weapon/001</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -557,7 +545,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:C1532"/>
+  <dimension ref="A1:C1529"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.625" style="3" customWidth="1"/>
@@ -606,7 +594,7 @@
         <v>134020003</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>8</v>
@@ -639,10 +627,10 @@
         <v>134020006</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -650,10 +638,10 @@
         <v>134020007</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -664,7 +652,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -672,53 +660,29 @@
         <v>134020009</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
-        <v>134020010</v>
-      </c>
-      <c r="B11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
-        <v>134020011</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
-        <v>134020012</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="1434" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1434" s="6"/>
+    </row>
+    <row r="1431" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1431" s="6"/>
+    </row>
+    <row r="1432" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1432" s="6"/>
+    </row>
+    <row r="1434" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1434" s="7"/>
     </row>
     <row r="1435" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1435" s="6"/>
-    </row>
-    <row r="1437" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1437" s="7"/>
+      <c r="B1435" s="1"/>
+    </row>
+    <row r="1436" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1436" s="1"/>
+    </row>
+    <row r="1437" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1437" s="1"/>
     </row>
     <row r="1438" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1438" s="1"/>
@@ -995,15 +959,6 @@
     </row>
     <row r="1529" spans="2:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1529" s="1"/>
-    </row>
-    <row r="1530" spans="2:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1530" s="1"/>
-    </row>
-    <row r="1531" spans="2:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1531" s="1"/>
-    </row>
-    <row r="1532" spans="2:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1532" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
